--- a/output/pdf_financials_xlsx/KBL.xlsx
+++ b/output/pdf_financials_xlsx/KBL.xlsx
@@ -2279,10 +2279,10 @@
         <v>5.857</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>9.423</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>23.355</v>
       </c>
     </row>
     <row r="35">
@@ -2389,10 +2389,10 @@
         <v>5.857</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>9.423</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>23.355</v>
       </c>
     </row>
     <row r="37">
@@ -3049,10 +3049,10 @@
         <v>42.731</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>56.003</v>
+        <v>46.58</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>110.911</v>
+        <v>87.556</v>
       </c>
     </row>
     <row r="49">
@@ -7339,22 +7339,22 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-6.691</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-7.168</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-7.397</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-9.391</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-10.648</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-15.722</v>
       </c>
     </row>
     <row r="125">
@@ -7394,22 +7394,22 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-6.691</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-7.168</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-7.397</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-9.391</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-10.648</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-15.722</v>
       </c>
     </row>
     <row r="126">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -28144,7 +28144,11 @@
           <t>Principal elements of lease payments (note 13)</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -29674,7 +29678,11 @@
           <t>Principle elements of lease payments</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -30558,7 +30566,11 @@
           <t>Principle elements of lease payments (note 13)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -31406,7 +31418,11 @@
           <t>Principle elements of lease payments (note 14)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -43134,7 +43150,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">

--- a/output/pdf_financials_xlsx/KBL.xlsx
+++ b/output/pdf_financials_xlsx/KBL.xlsx
@@ -834,52 +834,52 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>2.991</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>3.762</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>3.896</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>4.703</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>5.183</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>5.313</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>9.882999999999999</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>4.483</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>3.918</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>4.535</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>5.432</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>6.372</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>10.486</v>
       </c>
     </row>
     <row r="10">
@@ -904,10 +904,10 @@
         <v>107.885</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>5.183</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>130.958</v>
@@ -959,10 +959,10 @@
         <v>23.317</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>136.44</v>
+        <v>131.64</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>144.537</v>
+        <v>139.354</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>28.131</v>
@@ -1955,52 +1955,52 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2.157</v>
+        <v>7.504</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2.54</v>
+        <v>8.930999999999999</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2.628</v>
+        <v>8.566000000000001</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2.327</v>
+        <v>8.677</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2.14</v>
+        <v>8.105</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2.121</v>
+        <v>8.938000000000001</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>2.009</v>
+        <v>9.582000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.79</v>
+        <v>11.025</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.767</v>
+        <v>13.373</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>3.004</v>
+        <v>37.75</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>3.26</v>
+        <v>55.93</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>3.237</v>
+        <v>26.862</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>2.302</v>
+        <v>26.068</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.625</v>
+        <v>27.294</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>3.245</v>
+        <v>33.679</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>8.207000000000001</v>
+        <v>49.737</v>
       </c>
     </row>
     <row r="29">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9.834</v>
+        <v>15.181</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>16.877</v>
@@ -2052,10 +2052,10 @@
         <v>56.806</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>27.284</v>
+        <v>57.718</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>32.859</v>
+        <v>74.389</v>
       </c>
     </row>
     <row r="30">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>11.23462008613894</v>
+        <v>17.34317343173432</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>16.2199306109504</v>
@@ -2107,10 +2107,10 @@
         <v>17.70297054387255</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>7.302821934161114</v>
+        <v>15.44877130904234</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>6.483929783573019</v>
+        <v>14.67887192763667</v>
       </c>
     </row>
     <row r="31">
@@ -5989,52 +5989,52 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>7.504</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>8.930999999999999</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>8.566000000000001</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>8.677</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>8.105</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>8.938000000000001</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>9.582000000000001</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>11.025</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>13.373</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>18.875</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>27.965</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>26.862</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>26.068</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>27.294</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>33.679</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>49.737</v>
       </c>
     </row>
     <row r="101">
@@ -6649,52 +6649,52 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.397</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>1.353</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>1.899</v>
       </c>
     </row>
     <row r="113">
@@ -26600,7 +26600,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -26686,7 +26690,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -28498,7 +28502,11 @@
           <t>Proceeds from disposal of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -29864,7 +29872,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E235" s="5" t="n">
         <v>0.022</v>
       </c>
@@ -30664,7 +30676,11 @@
           <t>Depreciation of property, plant and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -30756,7 +30772,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -32474,7 +32490,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -33712,7 +33728,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -33808,7 +33828,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -35166,7 +35186,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -37450,7 +37474,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E315" s="5" t="n">
         <v>5.347</v>
       </c>
@@ -37542,7 +37570,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E316" s="5" t="n">
@@ -40510,7 +40538,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E349" s="5" t="n">
         <v>2.991</v>
       </c>
@@ -40934,7 +40966,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -41016,7 +41052,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -47666,7 +47702,11 @@
           <t>Depreciation of property, plant and equipment 6,053 4,484</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -47762,7 +47802,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -49176,7 +49216,11 @@
           <t>Depreciation of property, plant and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -49268,7 +49312,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -51710,7 +51754,11 @@
           <t>Occupancy costs (note 10)</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -52562,7 +52610,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>
@@ -52656,11 +52708,11 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E481" s="5" t="n">
-        <v>-2.157</v>
+        <v>2.157</v>
       </c>
       <c r="F481" s="5" t="n">
         <v>2.54</v>
@@ -53316,12 +53368,16 @@
           <t>Depreciation of property, plant and equipment $</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E488" s="5" t="n">
-        <v>-5.347</v>
+        <v>5.347</v>
       </c>
       <c r="F488" s="5" t="n">
-        <v>-5.666</v>
+        <v>5.666</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/KBL.xlsx
+++ b/output/pdf_financials_xlsx/KBL.xlsx
@@ -3486,49 +3486,49 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>58.217</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>63.341</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>75.622</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>100.129</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>115.293</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>166.941</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>36.051</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>272.288</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>329.007</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>366.136</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>378.599</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>407.896</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>456.204</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>569.9930000000001</v>
       </c>
     </row>
     <row r="57">
@@ -3541,49 +3541,49 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>24.36</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>30.246</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>36.447</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>42.157</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>48.974</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>53.683</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>64.383</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>102.675</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>150.271</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>173.075</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>198.759</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>229.04</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>264.526</v>
       </c>
     </row>
     <row r="58">
@@ -4332,25 +4332,25 @@
         <v>0</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>2.854</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>8.297000000000001</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>9.206</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>9.615</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>12.023</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>12.237</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>18.669</v>
       </c>
     </row>
     <row r="71">
@@ -4387,25 +4387,25 @@
         <v>0</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>2.854</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>8.297000000000001</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>9.206</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>9.615</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>12.023</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>12.237</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>8.394</v>
+        <v>27.063</v>
       </c>
     </row>
     <row r="72">
@@ -4607,25 +4607,25 @@
         <v>1.889</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>1.056</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>10.864</v>
+        <v>2.567</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>43.501</v>
+        <v>34.295</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>43.474</v>
+        <v>33.859</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>57.512</v>
+        <v>45.489</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>58.321</v>
+        <v>46.084</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>95.568</v>
+        <v>76.899</v>
       </c>
     </row>
     <row r="76">
@@ -4888,25 +4888,25 @@
         <v>0.212216065520098</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.3533826638477801</v>
+        <v>0.3677489177489178</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.3187639950829121</v>
+        <v>0.3610846157377417</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.2037167182579493</v>
+        <v>0.2531048653172461</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.2558371379048612</v>
+        <v>0.310300098560116</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.4027208466384989</v>
+        <v>0.4716478148952881</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.6534889737132479</v>
+        <v>0.7180945140461747</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.8674651719038142</v>
+        <v>0.9356387737588782</v>
       </c>
     </row>
     <row r="81">
@@ -6319,19 +6319,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-3.319</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>0.549</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-0.419</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-0.421</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-1.374</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>1.34</v>
@@ -6380,46 +6380,46 @@
         <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>1.661</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>1.105</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>1.237</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>-0.037</v>
+        <v>1.099</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>1.304</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>1.518</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>1.508</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>1.817</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>1.848</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>1.796</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>1.915</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>2.713</v>
       </c>
     </row>
     <row r="108">
@@ -6563,28 +6563,28 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="111">
@@ -6707,10 +6707,10 @@
         <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>0</v>
+        <v>-12.259</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0</v>
+        <v>4.317</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>0</v>
@@ -6725,13 +6725,13 @@
         <v>0</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>0</v>
+        <v>-56.774</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>0</v>
+        <v>-56.774</v>
       </c>
       <c r="K113" s="3" t="n">
-        <v>0</v>
+        <v>-4.7</v>
       </c>
       <c r="L113" s="3" t="n">
         <v>0</v>
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.679</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.244</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -6884,10 +6884,10 @@
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.184</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
@@ -6896,25 +6896,25 @@
         <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.106</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-1.439</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.493</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.495</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-0.326</v>
       </c>
     </row>
     <row r="117">
@@ -7183,10 +7183,10 @@
         <v>0</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-6.496</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-3.95</v>
       </c>
       <c r="Q121" s="3" t="n">
         <v>0</v>
@@ -9400,7 +9400,11 @@
           <t>Lease liabilities (note 13)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11964,7 +11968,11 @@
           <t>Lease liabilities (note 14)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -26776,7 +26784,11 @@
           <t>Accretion expense (note 10)</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -26864,7 +26876,11 @@
           <t>Employee share based compensation expense (note 25)</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -27242,7 +27258,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -28054,7 +28074,11 @@
           <t>Repurchase of shares (note 16)</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -28600,7 +28624,11 @@
           <t>Purchase of intangible assets (note 8)</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -29414,7 +29442,11 @@
           <t>Employee share based compensation expense</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -30964,7 +30996,11 @@
           <t>Accretion expense (note 11)</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -31726,7 +31762,11 @@
           <t>Purchase of intangible assets (note 9)</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -31820,7 +31860,11 @@
           <t>Acquisition of business (note 6)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -32680,7 +32724,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -33246,7 +33294,11 @@
           <t>Acquisition of business (note</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -34122,7 +34174,11 @@
           <t>Employee share based compensation expense</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -35284,7 +35340,11 @@
           <t>Purchase of intangible assets (note 8)</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -36700,7 +36760,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -36792,7 +36856,11 @@
           <t>Change in non-cash balances relating to operations (note 21)</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -37756,7 +37824,11 @@
           <t>Change in non-cash balances relating to operations (note 17)</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -37848,7 +37920,11 @@
           <t>Acquisition of business (note 5)</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -38036,7 +38112,11 @@
           <t>Acquisition of business (note 5)</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -38604,7 +38684,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E327" s="5" t="n">
         <v>-0.679</v>
       </c>
@@ -38698,7 +38782,11 @@
           <t>Acquisition of businesses (note 5)</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -38984,7 +39072,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E331" s="5" t="n">
         <v>-0.125</v>
       </c>
@@ -39078,7 +39170,11 @@
           <t>change in non-cash balances relating to operations (note 13)</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E332" s="5" t="n">
         <v>-3.319</v>
       </c>
@@ -39554,7 +39650,11 @@
           <t>Acquisition of business (note 2)</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -49774,7 +49874,11 @@
           <t>Current income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
